--- a/artfynd/A 37930-2023 artfynd.xlsx
+++ b/artfynd/A 37930-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113405896</v>
+        <v>113405891</v>
       </c>
       <c r="B2" t="n">
-        <v>90589</v>
+        <v>91298</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>760</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296161</v>
+        <v>296150</v>
       </c>
       <c r="R2" t="n">
-        <v>6520720</v>
+        <v>6520732</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -780,7 +780,7 @@
         <v>113405894</v>
       </c>
       <c r="B3" t="n">
-        <v>91302</v>
+        <v>91318</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113405891</v>
+        <v>113405896</v>
       </c>
       <c r="B4" t="n">
-        <v>91282</v>
+        <v>90605</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296150</v>
+        <v>296161</v>
       </c>
       <c r="R4" t="n">
-        <v>6520732</v>
+        <v>6520720</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 37930-2023 artfynd.xlsx
+++ b/artfynd/A 37930-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113405891</v>
+        <v>113405896</v>
       </c>
       <c r="B2" t="n">
-        <v>91298</v>
+        <v>90605</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296150</v>
+        <v>296161</v>
       </c>
       <c r="R2" t="n">
-        <v>6520732</v>
+        <v>6520720</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113405894</v>
+        <v>113405891</v>
       </c>
       <c r="B3" t="n">
-        <v>91318</v>
+        <v>91298</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296148</v>
+        <v>296150</v>
       </c>
       <c r="R3" t="n">
         <v>6520732</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113405896</v>
+        <v>113405894</v>
       </c>
       <c r="B4" t="n">
-        <v>90605</v>
+        <v>91318</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>760</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296161</v>
+        <v>296148</v>
       </c>
       <c r="R4" t="n">
-        <v>6520720</v>
+        <v>6520732</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 37930-2023 artfynd.xlsx
+++ b/artfynd/A 37930-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113405896</v>
       </c>
       <c r="B2" t="n">
-        <v>90605</v>
+        <v>90617</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>113405891</v>
       </c>
       <c r="B3" t="n">
-        <v>91298</v>
+        <v>91310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>113405894</v>
       </c>
       <c r="B4" t="n">
-        <v>91318</v>
+        <v>91330</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 37930-2023 artfynd.xlsx
+++ b/artfynd/A 37930-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113405896</v>
+        <v>113405891</v>
       </c>
       <c r="B2" t="n">
-        <v>90617</v>
+        <v>91310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>760</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296161</v>
+        <v>296150</v>
       </c>
       <c r="R2" t="n">
-        <v>6520720</v>
+        <v>6520732</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113405891</v>
+        <v>113405894</v>
       </c>
       <c r="B3" t="n">
-        <v>91310</v>
+        <v>91330</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296150</v>
+        <v>296148</v>
       </c>
       <c r="R3" t="n">
         <v>6520732</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113405894</v>
+        <v>113405896</v>
       </c>
       <c r="B4" t="n">
-        <v>91330</v>
+        <v>90617</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296148</v>
+        <v>296161</v>
       </c>
       <c r="R4" t="n">
-        <v>6520732</v>
+        <v>6520720</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 37930-2023 artfynd.xlsx
+++ b/artfynd/A 37930-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113405891</v>
       </c>
       <c r="B2" t="n">
-        <v>91310</v>
+        <v>91332</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113405894</v>
+        <v>113405896</v>
       </c>
       <c r="B3" t="n">
-        <v>91330</v>
+        <v>90639</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296148</v>
+        <v>296161</v>
       </c>
       <c r="R3" t="n">
-        <v>6520732</v>
+        <v>6520720</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113405896</v>
+        <v>113405894</v>
       </c>
       <c r="B4" t="n">
-        <v>90617</v>
+        <v>91352</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>760</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296161</v>
+        <v>296148</v>
       </c>
       <c r="R4" t="n">
-        <v>6520720</v>
+        <v>6520732</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 37930-2023 artfynd.xlsx
+++ b/artfynd/A 37930-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113405891</v>
+        <v>113405894</v>
       </c>
       <c r="B2" t="n">
-        <v>91332</v>
+        <v>91356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296150</v>
+        <v>296148</v>
       </c>
       <c r="R2" t="n">
         <v>6520732</v>
@@ -780,7 +780,7 @@
         <v>113405896</v>
       </c>
       <c r="B3" t="n">
-        <v>90639</v>
+        <v>90643</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113405894</v>
+        <v>113405891</v>
       </c>
       <c r="B4" t="n">
-        <v>91352</v>
+        <v>91336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296148</v>
+        <v>296150</v>
       </c>
       <c r="R4" t="n">
         <v>6520732</v>

--- a/artfynd/A 37930-2023 artfynd.xlsx
+++ b/artfynd/A 37930-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113405894</v>
+        <v>113405896</v>
       </c>
       <c r="B2" t="n">
-        <v>91356</v>
+        <v>90643</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296148</v>
+        <v>296161</v>
       </c>
       <c r="R2" t="n">
-        <v>6520732</v>
+        <v>6520720</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113405896</v>
+        <v>113405891</v>
       </c>
       <c r="B3" t="n">
-        <v>90643</v>
+        <v>91336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296161</v>
+        <v>296150</v>
       </c>
       <c r="R3" t="n">
-        <v>6520720</v>
+        <v>6520732</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113405891</v>
+        <v>113405894</v>
       </c>
       <c r="B4" t="n">
-        <v>91336</v>
+        <v>91356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296150</v>
+        <v>296148</v>
       </c>
       <c r="R4" t="n">
         <v>6520732</v>

--- a/artfynd/A 37930-2023 artfynd.xlsx
+++ b/artfynd/A 37930-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113405896</v>
+        <v>113405894</v>
       </c>
       <c r="B2" t="n">
-        <v>90643</v>
+        <v>91362</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>760</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296161</v>
+        <v>296148</v>
       </c>
       <c r="R2" t="n">
-        <v>6520720</v>
+        <v>6520732</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -780,7 +780,7 @@
         <v>113405891</v>
       </c>
       <c r="B3" t="n">
-        <v>91336</v>
+        <v>91342</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113405894</v>
+        <v>113405896</v>
       </c>
       <c r="B4" t="n">
-        <v>91356</v>
+        <v>90649</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296148</v>
+        <v>296161</v>
       </c>
       <c r="R4" t="n">
-        <v>6520732</v>
+        <v>6520720</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 37930-2023 artfynd.xlsx
+++ b/artfynd/A 37930-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113405894</v>
+        <v>113405891</v>
       </c>
       <c r="B2" t="n">
-        <v>91362</v>
+        <v>91342</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296148</v>
+        <v>296150</v>
       </c>
       <c r="R2" t="n">
         <v>6520732</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113405891</v>
+        <v>113405894</v>
       </c>
       <c r="B3" t="n">
-        <v>91342</v>
+        <v>91362</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296150</v>
+        <v>296148</v>
       </c>
       <c r="R3" t="n">
         <v>6520732</v>

--- a/artfynd/A 37930-2023 artfynd.xlsx
+++ b/artfynd/A 37930-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113405891</v>
       </c>
       <c r="B2" t="n">
-        <v>91342</v>
+        <v>91349</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113405894</v>
+        <v>113405896</v>
       </c>
       <c r="B3" t="n">
-        <v>91362</v>
+        <v>90656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296148</v>
+        <v>296161</v>
       </c>
       <c r="R3" t="n">
-        <v>6520732</v>
+        <v>6520720</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113405896</v>
+        <v>113405894</v>
       </c>
       <c r="B4" t="n">
-        <v>90649</v>
+        <v>91369</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>760</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296161</v>
+        <v>296148</v>
       </c>
       <c r="R4" t="n">
-        <v>6520720</v>
+        <v>6520732</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 37930-2023 artfynd.xlsx
+++ b/artfynd/A 37930-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113405891</v>
       </c>
       <c r="B2" t="n">
-        <v>91349</v>
+        <v>91354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>113405896</v>
       </c>
       <c r="B3" t="n">
-        <v>90656</v>
+        <v>90661</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>113405894</v>
       </c>
       <c r="B4" t="n">
-        <v>91369</v>
+        <v>91374</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 37930-2023 artfynd.xlsx
+++ b/artfynd/A 37930-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113405891</v>
       </c>
       <c r="B2" t="n">
-        <v>91354</v>
+        <v>91382</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>113405896</v>
       </c>
       <c r="B3" t="n">
-        <v>90661</v>
+        <v>90692</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>113405894</v>
       </c>
       <c r="B4" t="n">
-        <v>91374</v>
+        <v>91402</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 37930-2023 artfynd.xlsx
+++ b/artfynd/A 37930-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113405896</v>
+        <v>113405894</v>
       </c>
       <c r="B3" t="n">
-        <v>90692</v>
+        <v>91402</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296161</v>
+        <v>296148</v>
       </c>
       <c r="R3" t="n">
-        <v>6520720</v>
+        <v>6520732</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113405894</v>
+        <v>113405896</v>
       </c>
       <c r="B4" t="n">
-        <v>91402</v>
+        <v>90693</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296148</v>
+        <v>296161</v>
       </c>
       <c r="R4" t="n">
-        <v>6520732</v>
+        <v>6520720</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 37930-2023 artfynd.xlsx
+++ b/artfynd/A 37930-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37930-2023 artfynd.xlsx
+++ b/artfynd/A 37930-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113405891</v>
+        <v>111508799</v>
       </c>
       <c r="B2" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,20 +703,30 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Liveröd, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296150</v>
+        <v>296142</v>
       </c>
       <c r="R2" t="n">
-        <v>6520732</v>
+        <v>6520677</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +750,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Återkommande sedan första besök 2008 på lokalen- förutom åren 2018-2020</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,49 +775,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Suzi B Jagre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Suzi B Jagre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113405894</v>
+        <v>113405891</v>
       </c>
       <c r="B3" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,7 +822,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296148</v>
+        <v>296150</v>
       </c>
       <c r="R3" t="n">
         <v>6520732</v>
@@ -879,15 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113405896</v>
+        <v>113405894</v>
       </c>
       <c r="B4" t="n">
-        <v>91623</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Liveröd, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296161</v>
+        <v>296148</v>
       </c>
       <c r="R4" t="n">
-        <v>6520720</v>
+        <v>6520732</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,7 +963,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -985,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111508799</v>
+        <v>113405896</v>
       </c>
       <c r="B5" t="n">
-        <v>91707</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,47 +992,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>4368</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Liveröd, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296142</v>
+        <v>296161</v>
       </c>
       <c r="R5" t="n">
-        <v>6520677</v>
+        <v>6520720</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1065,17 +1049,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Återkommande sedan första besök 2008 på lokalen- förutom åren 2018-2020</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1084,18 +1063,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Suzi B Jagre</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Suzi B Jagre</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 37930-2023 artfynd.xlsx
+++ b/artfynd/A 37930-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111508799</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405891</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405894</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,8 +1099,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405896</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>